--- a/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8A8834-9402-4107-AAB2-F1E9AB6F6574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538AA09A-2BFE-4298-942E-DC7134FD0818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538AA09A-2BFE-4298-942E-DC7134FD0818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC559380-E052-422B-9509-31E263C1FB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -955,22 +955,22 @@
                   <c:v>132.31000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>138.92550000000003</c:v>
+                  <c:v>136.27930000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>154.80270000000002</c:v>
+                  <c:v>157.44890000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>170.67990000000003</c:v>
+                  <c:v>189.20330000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>187.88020000000003</c:v>
+                  <c:v>218.31150000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>210.37290000000007</c:v>
+                  <c:v>239.48110000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>228.89630000000005</c:v>
+                  <c:v>255.35830000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6038,7 +6038,7 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.45">
       <c r="D3" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" s="10">
         <v>300</v>
@@ -6050,7 +6050,7 @@
         <v>115</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.45">
@@ -6070,7 +6070,7 @@
     <row r="5" spans="1:39" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="str">
         <f>VLOOKUP(D3,$C$9:$E$999,2,FALSE)</f>
-        <v>base</v>
+        <v>high</v>
       </c>
       <c r="E5" s="1">
         <f>VLOOKUP(D3,$C$9:$E$999,3,FALSE)</f>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="H14" s="3" t="str">
         <f>VLOOKUP($D$5,$N$3:$O$5,2,FALSE)</f>
-        <v>C4</v>
+        <v>C1</v>
       </c>
       <c r="I14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
@@ -6368,27 +6368,27 @@
       </c>
       <c r="J14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="K14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="L14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="M14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="N14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="T14" s="8">
         <f>S11</f>
@@ -6396,27 +6396,27 @@
       </c>
       <c r="U14" s="8">
         <f t="shared" ref="U14:Z14" si="4">$S$11*J14</f>
-        <v>138.92550000000003</v>
+        <v>136.27930000000003</v>
       </c>
       <c r="V14" s="8">
         <f t="shared" si="4"/>
-        <v>154.80270000000002</v>
+        <v>157.44890000000004</v>
       </c>
       <c r="W14" s="8">
         <f t="shared" si="4"/>
-        <v>170.67990000000003</v>
+        <v>189.20330000000004</v>
       </c>
       <c r="X14" s="8">
         <f t="shared" si="4"/>
-        <v>187.88020000000003</v>
+        <v>218.31150000000005</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="4"/>
-        <v>210.37290000000007</v>
+        <v>239.48110000000005</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="4"/>
-        <v>228.89630000000005</v>
+        <v>255.35830000000004</v>
       </c>
       <c r="AG14">
         <v>6</v>
@@ -6465,23 +6465,23 @@
       </c>
       <c r="K15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="M15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="N15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>0.83</v>
+        <v>0.94</v>
       </c>
       <c r="O15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="AG15">
         <v>7</v>
@@ -6613,62 +6613,62 @@
       </c>
       <c r="I18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="M18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="S18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="T18" s="6">
         <f t="shared" ref="T18:Z20" si="7">I18*T$14</f>
-        <v>0</v>
+        <v>1.3231000000000004</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.3627930000000004</v>
       </c>
       <c r="V18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.5744890000000005</v>
       </c>
       <c r="W18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.6760990000000007</v>
       </c>
       <c r="X18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.5493450000000015</v>
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.5792440000000028</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.767915000000002</v>
       </c>
       <c r="AA18" t="s">
         <v>17</v>
@@ -6694,62 +6694,62 @@
       </c>
       <c r="I19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="J19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="K19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="L19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="N19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.28999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="O19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="S19" s="10" t="s">
         <v>19</v>
       </c>
       <c r="T19" s="6">
         <f t="shared" si="7"/>
-        <v>48.95470000000001</v>
+        <v>46.308500000000009</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="7"/>
-        <v>48.623925000000007</v>
+        <v>43.609376000000012</v>
       </c>
       <c r="V19" s="6">
         <f t="shared" si="7"/>
-        <v>52.632918000000011</v>
+        <v>47.234670000000008</v>
       </c>
       <c r="W19" s="6">
         <f t="shared" si="7"/>
-        <v>56.324367000000017</v>
+        <v>54.868957000000009</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" si="7"/>
-        <v>56.364060000000009</v>
+        <v>63.310335000000009</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="7"/>
-        <v>61.008141000000016</v>
+        <v>71.844330000000014</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="7"/>
-        <v>68.668890000000019</v>
+        <v>79.161073000000016</v>
       </c>
       <c r="AA19" t="s">
         <v>17</v>
@@ -6774,11 +6774,11 @@
       </c>
       <c r="I20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="J20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="K20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
@@ -6786,50 +6786,50 @@
       </c>
       <c r="L20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.57999999999999996</v>
+        <v>0.54</v>
       </c>
       <c r="N20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.56000000000000005</v>
+        <v>0.53</v>
       </c>
       <c r="O20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="S20" s="10" t="s">
         <v>22</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="7"/>
-        <v>78.062900000000013</v>
+        <v>80.709100000000021</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="7"/>
-        <v>81.966045000000008</v>
+        <v>84.493166000000016</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="7"/>
-        <v>91.333593000000008</v>
+        <v>92.894851000000017</v>
       </c>
       <c r="W20" s="6">
         <f t="shared" si="7"/>
-        <v>98.994342000000017</v>
+        <v>105.95384800000004</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" si="7"/>
-        <v>108.970516</v>
+        <v>117.88821000000003</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="7"/>
-        <v>117.80882400000006</v>
+        <v>126.92498300000004</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="7"/>
-        <v>123.60400200000004</v>
+        <v>135.33989900000003</v>
       </c>
       <c r="AA20" t="s">
         <v>17</v>
@@ -6858,27 +6858,27 @@
       </c>
       <c r="J21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="L21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.06</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>7.0000000000000007E-2</v>
+        <v>0.17</v>
       </c>
       <c r="N21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="O21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="S21" s="10" t="s">
         <v>24</v>
@@ -6932,27 +6932,27 @@
       </c>
       <c r="U22" s="6">
         <f t="shared" si="9"/>
-        <v>4.3662300000000016</v>
+        <v>4.2074580000000026</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" si="9"/>
-        <v>6.8668889999999863</v>
+        <v>13.350079000000022</v>
       </c>
       <c r="W22" s="6">
         <f t="shared" si="9"/>
-        <v>11.391890999999987</v>
+        <v>24.411194999999992</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" si="9"/>
-        <v>18.576324</v>
+        <v>33.143655000000024</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="9"/>
-        <v>27.586635000000001</v>
+        <v>36.742486999999983</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="9"/>
-        <v>32.654107999999979</v>
+        <v>36.888027999999991</v>
       </c>
       <c r="AA22" t="s">
         <v>17</v>
@@ -6976,23 +6976,23 @@
       </c>
       <c r="V23" s="25">
         <f>$S$12*K15</f>
-        <v>2.0563199999999999</v>
+        <v>1.9278</v>
       </c>
       <c r="W23" s="25">
         <f t="shared" ref="W23:Z23" si="10">$S$12*L15</f>
-        <v>1.9706399999999999</v>
+        <v>1.90638</v>
       </c>
       <c r="X23" s="25">
         <f t="shared" si="10"/>
-        <v>1.7992799999999998</v>
+        <v>1.9706399999999999</v>
       </c>
       <c r="Y23" s="25">
         <f t="shared" si="10"/>
-        <v>1.7778599999999998</v>
+        <v>2.0134799999999999</v>
       </c>
       <c r="Z23" s="25">
         <f t="shared" si="10"/>
-        <v>1.7136</v>
+        <v>2.0563199999999999</v>
       </c>
       <c r="AA23" s="23" t="s">
         <v>17</v>
